--- a/examples/comparison-cached-values.xlsx
+++ b/examples/comparison-cached-values.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>example\a.xlsx</t>
+          <t>examples\a.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>example\b.xlsx</t>
+          <t>examples\b.xlsx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -517,15 +517,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>OnlyA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Only in file1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OnlyB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Only in file2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Sheet1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Differences found</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>df-Sheet1</t>
         </is>
